--- a/REGISTRY.xlsx
+++ b/REGISTRY.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已发布Skill登记表(首批300)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="github渠道Skill登记表(300)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L301"/>
+  <dimension ref="A1:N301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -462,8 +462,10 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="65" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,10 +521,20 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>所属渠道</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>渠道落地页链接</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>相对路径</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>发布状态</t>
         </is>
@@ -577,10 +589,20 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>skills/ecom-ai-super-orchestrator/SKILL.md</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -635,10 +657,20 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
           <t>skills/1688-factory-spec-image-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -693,10 +725,20 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>skills/runway-cinema-ad-tvc-generator/SKILL.md</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -751,10 +793,20 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-listing-compliance-image-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -809,10 +861,20 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>skills/photoroom-bg-swap-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -867,10 +929,20 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>skills/clothing-sku-recolor-ai-fast/SKILL.md</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -925,10 +997,20 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>skills/ecom-detail-page-builder-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -983,10 +1065,20 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>skills/detail-page-structure-clone-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1041,10 +1133,20 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>skills/douyin-shop-high-ctr-image-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1099,10 +1201,20 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>skills/douyin-viral-hook-video-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1157,10 +1269,20 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>skills/ecom-image-all-in-one-generator/SKILL.md</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1215,10 +1337,20 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
           <t>skills/ecom-video-all-in-one-generator/SKILL.md</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1273,10 +1405,20 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>skills/gpt-image-2-crossborder-finetuned/SKILL.md</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1331,10 +1473,20 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
           <t>skills/grok-meme-viral-video-clone/SKILL.md</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1389,10 +1541,20 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>skills/grok-trendy-ecom-video-creator/SKILL.md</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1447,10 +1609,20 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>skills/happyhorse-camera-movement-clone/SKILL.md</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1505,10 +1677,20 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
           <t>skills/happyhorse-seed-product-showcase/SKILL.md</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1563,10 +1745,20 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t>skills/ecom-image-ad-creative-engine/SKILL.md</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1621,10 +1813,20 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t>skills/lossless-image-compressor-fast/SKILL.md</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1679,10 +1881,20 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
           <t>skills/meitu-image-object-eraser-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1737,10 +1949,20 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>skills/dreamina-commercial-image-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1795,10 +2017,20 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
           <t>skills/image-multilingual-text-editor/SKILL.md</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1853,10 +2085,20 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t>skills/crossborder-image-translate-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1911,10 +2153,20 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
           <t>skills/image-ab-testing-variations-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -1969,10 +2221,20 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t>skills/brand-watermark-batch-stamper/SKILL.md</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2027,10 +2289,20 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
           <t>skills/jd-3c-appliance-image-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2085,10 +2357,20 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
           <t>skills/kling-3-viral-video-clone-master/SKILL.md</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2143,10 +2425,20 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t>skills/kling-3-sales-video-engine/SKILL.md</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2201,10 +2493,20 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
           <t>skills/lazada-lazmall-local-image-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2259,10 +2561,20 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
           <t>skills/viral-main-image-clone-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2317,10 +2629,20 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
           <t>skills/main-image-ctr-optimizer/SKILL.md</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2375,10 +2697,20 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
           <t>skills/larkai-main-image-carousel-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2433,10 +2765,20 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
           <t>skills/ecom-marketing-assets-toolkit-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2491,10 +2833,20 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
           <t>skills/ecom-multimedia-repair-toolbox/SKILL.md</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2549,10 +2901,20 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
           <t>skills/minimax-h3-ugc-seed-video-clone/SKILL.md</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2607,10 +2969,20 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
           <t>skills/minimax-h3-lip-sync-sales-video/SKILL.md</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2665,10 +3037,20 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
           <t>skills/crossborder-model-faceswap-global/SKILL.md</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2723,10 +3105,20 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
           <t>skills/weshop-virtual-fitting-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2781,10 +3173,20 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
           <t>skills/model-multi-pose-catalog-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2839,10 +3241,20 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
           <t>skills/nano-banana-2-ctr-ad-assets/SKILL.md</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2897,10 +3309,20 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
           <t>skills/pinduoduo-promo-banner-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -2955,10 +3377,20 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
           <t>skills/pod-print-on-demand-assets-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3013,10 +3445,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
           <t>skills/printify-pod-3d-mockup-applier/SKILL.md</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3071,10 +3513,20 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
           <t>skills/pod-pattern-hd-vector-extractor/SKILL.md</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3129,10 +3581,20 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
           <t>skills/pod-pattern-creative-variations-ai/SKILL.md</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3187,10 +3649,20 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
           <t>skills/product-swap-scene-retainer/SKILL.md</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3245,10 +3717,20 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
           <t>skills/canva-ecom-promo-poster-creator/SKILL.md</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3303,10 +3785,20 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
           <t>skills/sales-video-hook-script-ai/SKILL.md</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3361,10 +3853,20 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
           <t>skills/capcut-sales-video-auto-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3419,10 +3921,20 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
           <t>skills/flairai-luxury-scene-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3477,10 +3989,20 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
           <t>skills/seedance-2-rhythm-video-clone/SKILL.md</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3535,10 +4057,20 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
           <t>skills/seedance-2-dynamic-product-showcase/SKILL.md</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3593,10 +4125,20 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
           <t>skills/seedance-25-viral-emotion-clone/SKILL.md</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3651,10 +4193,20 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
           <t>skills/seedance-25-cinema-product-commercial/SKILL.md</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3709,10 +4261,20 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
           <t>skills/seedream-5-lite-chinese-typeset/SKILL.md</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3767,10 +4329,20 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
           <t>skills/seedream-5-pro-commercial-ecom/SKILL.md</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3825,10 +4397,20 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-fast-fashion-lookbook-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3883,10 +4465,20 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
           <t>skills/wechat-channels-viral-video-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3941,10 +4533,20 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-southeast-asia-image-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -3999,10 +4601,20 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
           <t>skills/video-storyboard-director-ai/SKILL.md</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4057,10 +4669,20 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
           <t>skills/taobao-tmall-listing-image-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4115,10 +4737,20 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-multi-sku-discount-image-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4173,10 +4805,20 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-high-ctr-cover-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4231,10 +4873,20 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-ugc-viral-video-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4289,10 +4941,20 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
           <t>skills/video-feed-ad-assets-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4347,10 +5009,20 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
           <t>skills/lalal-video-audio-extractor-hd/SKILL.md</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4405,10 +5077,20 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
           <t>skills/video-actor-role-swap-ai/SKILL.md</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4463,10 +5145,20 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
           <t>skills/video-subtitle-eraser-inpaint/SKILL.md</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4521,10 +5213,20 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
           <t>skills/heygen-video-dubbing-multilingual/SKILL.md</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4579,10 +5281,20 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
           <t>skills/topaz-video-upscale-60fps-hd/SKILL.md</t>
         </is>
       </c>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4637,10 +5349,20 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
           <t>skills/video-watermark-remover-clean/SKILL.md</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="N72" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4695,10 +5417,20 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
           <t>skills/vidu-q2-fast-pace-video-clone/SKILL.md</t>
         </is>
       </c>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4753,10 +5485,20 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
           <t>skills/vidu-q2-product-consistency-sales/SKILL.md</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4811,10 +5553,20 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
           <t>skills/vidu-q3-stopmotion-unboxing-clone/SKILL.md</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4869,10 +5621,20 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
           <t>skills/vidu-q3-jewelry-texture-commercial/SKILL.md</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4927,10 +5689,20 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
           <t>skills/kling-viral-video-clone-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -4985,10 +5757,20 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
           <t>skills/viral-video-remake-toolkit-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5043,10 +5825,20 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
           <t>skills/wanx-3-guangguang-viral-clone/SKILL.md</t>
         </is>
       </c>
-      <c r="L79" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5101,10 +5893,20 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
           <t>skills/wanx-3-taobao-mainvideo-engine/SKILL.md</t>
         </is>
       </c>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5159,10 +5961,20 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
           <t>skills/batch-white-background-cleaner/SKILL.md</t>
         </is>
       </c>
-      <c r="L81" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5217,10 +6029,20 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
           <t>skills/rednote-aesthetic-video-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5275,10 +6097,20 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
           <t>skills/youtube-product-review-video-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L83" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5333,10 +6165,20 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
           <t>skills/ali1688-factory-sourcing-expert/SKILL.md</t>
         </is>
       </c>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="N84" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5391,10 +6233,20 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
           <t>skills/helium10-asin-spy-analyzer/SKILL.md</t>
         </is>
       </c>
-      <c r="L85" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5449,10 +6301,20 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
           <t>skills/sellersprite-keyword-blueocean-picker/SKILL.md</t>
         </is>
       </c>
-      <c r="L86" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5507,10 +6369,20 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
           <t>skills/junglescout-market-niche-assessor/SKILL.md</t>
         </is>
       </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5565,10 +6437,20 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-hot-trend-hunter-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5623,10 +6505,20 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
           <t>skills/bilibili-deep-review-social-ops/SKILL.md</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr">
+      <c r="N89" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5681,10 +6573,20 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
           <t>skills/chanmama-creator-data-engine-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="N90" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5739,10 +6641,20 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
           <t>skills/door-outfit-change-viral-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L91" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5797,10 +6709,20 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
           <t>skills/douyin-bluesea-hot-product-collector/SKILL.md</t>
         </is>
       </c>
-      <c r="L92" s="2" t="inlineStr">
+      <c r="N92" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5855,10 +6777,20 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
           <t>skills/douyin-1688-fast-listing-copilot/SKILL.md</t>
         </is>
       </c>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="N93" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5913,10 +6845,20 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
           <t>skills/douyin-trending-social-director/SKILL.md</t>
         </is>
       </c>
-      <c r="L94" s="2" t="inlineStr">
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -5971,10 +6913,20 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
           <t>skills/douyin-viral-video-dropship-distributor/SKILL.md</t>
         </is>
       </c>
-      <c r="L95" s="2" t="inlineStr">
+      <c r="N95" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6029,10 +6981,20 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
           <t>skills/duo-character-viral-video-sync/SKILL.md</t>
         </is>
       </c>
-      <c r="L96" s="2" t="inlineStr">
+      <c r="N96" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6087,10 +7049,20 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
           <t>skills/crossborder-sourcing-copilot-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L97" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6145,10 +7117,20 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
           <t>skills/image-deai-photorealistic-hd/SKILL.md</t>
         </is>
       </c>
-      <c r="L98" s="2" t="inlineStr">
+      <c r="N98" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6203,10 +7185,20 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
           <t>skills/topaz-image-upscale-ultra-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L99" s="2" t="inlineStr">
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6261,10 +7253,20 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
           <t>skills/ai-image-watermark-cleaner-hd/SKILL.md</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr">
+      <c r="N100" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6319,10 +7321,20 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
           <t>skills/clothing-mannequin-to-model-hd/SKILL.md</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr">
+      <c r="N101" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6377,10 +7389,20 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
           <t>skills/model-skin-photorealistic-enhancer/SKILL.md</t>
         </is>
       </c>
-      <c r="L102" s="2" t="inlineStr">
+      <c r="N102" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6435,10 +7457,20 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
           <t>skills/qiangua-rednote-growth-scout/SKILL.md</t>
         </is>
       </c>
-      <c r="L103" s="2" t="inlineStr">
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6493,10 +7525,20 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
           <t>skills/chuhaijiang-shopee-bluesea-hunter/SKILL.md</t>
         </is>
       </c>
-      <c r="L104" s="2" t="inlineStr">
+      <c r="N104" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6551,10 +7593,20 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-cross-site-expansion-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L105" s="2" t="inlineStr">
+      <c r="N105" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6609,10 +7661,20 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sourcing-decision-matrix/SKILL.md</t>
         </is>
       </c>
-      <c r="L106" s="2" t="inlineStr">
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6667,10 +7729,20 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-hot-product-intercept-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L107" s="2" t="inlineStr">
+      <c r="N107" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6725,10 +7797,20 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
           <t>skills/feigua-shortvideo-monitor-engine/SKILL.md</t>
         </is>
       </c>
-      <c r="L108" s="2" t="inlineStr">
+      <c r="N108" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6783,10 +7865,20 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
           <t>skills/linkfox-tiktok-bluesea-scout/SKILL.md</t>
         </is>
       </c>
-      <c r="L109" s="2" t="inlineStr">
+      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6841,10 +7933,20 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-decision-matrix-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6899,10 +8001,20 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
           <t>skills/fastmoss-influencer-roi-scout/SKILL.md</t>
         </is>
       </c>
-      <c r="L111" s="2" t="inlineStr">
+      <c r="N111" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -6957,10 +8069,20 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
           <t>skills/echotik-product-viral-analyst/SKILL.md</t>
         </is>
       </c>
-      <c r="L112" s="2" t="inlineStr">
+      <c r="N112" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7015,10 +8137,20 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-viral-trends-radar-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L113" s="2" t="inlineStr">
+      <c r="N113" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7073,10 +8205,20 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shortvideo-script-clone-expert/SKILL.md</t>
         </is>
       </c>
-      <c r="L114" s="2" t="inlineStr">
+      <c r="N114" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7131,10 +8273,20 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
           <t>skills/cinema-tvc-product-film-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L115" s="2" t="inlineStr">
+      <c r="N115" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7189,10 +8341,20 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
           <t>skills/product-video-super-resolution-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L116" s="2" t="inlineStr">
+      <c r="N116" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7247,10 +8409,20 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
           <t>skills/kids-clothing-viral-video-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L117" s="2" t="inlineStr">
+      <c r="N117" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7305,10 +8477,20 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
           <t>skills/mens-clothing-viral-video-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L118" s="2" t="inlineStr">
+      <c r="N118" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7363,10 +8545,20 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
           <t>skills/womens-clothing-viral-video-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L119" s="2" t="inlineStr">
+      <c r="N119" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7421,10 +8613,20 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
           <t>skills/ecom-standard-workflow-app-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L120" s="2" t="inlineStr">
+      <c r="N120" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7479,10 +8681,20 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
           <t>skills/weshop-ghost-mannequin-to-model/SKILL.md</t>
         </is>
       </c>
-      <c r="L121" s="2" t="inlineStr">
+      <c r="N121" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7537,10 +8749,20 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
           <t>skills/vmodel-flatlay-garment-wearer/SKILL.md</t>
         </is>
       </c>
-      <c r="L122" s="2" t="inlineStr">
+      <c r="N122" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7595,10 +8817,20 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
           <t>skills/kreado-global-ethnicity-fitter/SKILL.md</t>
         </is>
       </c>
-      <c r="L123" s="2" t="inlineStr">
+      <c r="N123" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7653,10 +8885,20 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
           <t>skills/onmodel-shopify-face-swapper/SKILL.md</t>
         </is>
       </c>
-      <c r="L124" s="2" t="inlineStr">
+      <c r="N124" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7711,10 +8953,20 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
           <t>skills/lalaland-plussize-body-tryon/SKILL.md</t>
         </is>
       </c>
-      <c r="L125" s="2" t="inlineStr">
+      <c r="N125" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7769,10 +9021,20 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
           <t>skills/boutique9-luxury-texture-tryon/SKILL.md</t>
         </is>
       </c>
-      <c r="L126" s="2" t="inlineStr">
+      <c r="N126" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7827,10 +9089,20 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-fast-fashion-lookbook-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L127" s="2" t="inlineStr">
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7885,10 +9157,20 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
           <t>skills/footwear-handbag-virtual-stager/SKILL.md</t>
         </is>
       </c>
-      <c r="L128" s="2" t="inlineStr">
+      <c r="N128" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -7943,10 +9225,20 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
           <t>skills/swimwear-lingerie-realistic-fit/SKILL.md</t>
         </is>
       </c>
-      <c r="L129" s="2" t="inlineStr">
+      <c r="N129" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8001,10 +9293,20 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
           <t>skills/kids-apparel-cute-model-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L130" s="2" t="inlineStr">
+      <c r="N130" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8059,10 +9361,20 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
           <t>skills/photoroom-ecom-studio-bg-swap/SKILL.md</t>
         </is>
       </c>
-      <c r="L131" s="2" t="inlineStr">
+      <c r="N131" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8117,10 +9429,20 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
           <t>skills/clipdrop-4k-upscale-denoiser/SKILL.md</t>
         </is>
       </c>
-      <c r="L132" s="2" t="inlineStr">
+      <c r="N132" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8175,10 +9497,20 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
           <t>skills/pixelcut-mobile-shot-enhancer/SKILL.md</t>
         </is>
       </c>
-      <c r="L133" s="2" t="inlineStr">
+      <c r="N133" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8233,10 +9565,20 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
           <t>skills/picwish-batch-cutout-watermark-wipe/SKILL.md</t>
         </is>
       </c>
-      <c r="L134" s="2" t="inlineStr">
+      <c r="N134" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8291,10 +9633,20 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
           <t>skills/cosmetics-commercial-lighting-stage/SKILL.md</t>
         </is>
       </c>
-      <c r="L135" s="2" t="inlineStr">
+      <c r="N135" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8349,10 +9701,20 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
           <t>skills/vanceai-legacy-product-restorer/SKILL.md</t>
         </is>
       </c>
-      <c r="L136" s="2" t="inlineStr">
+      <c r="N136" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8407,10 +9769,20 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
           <t>skills/glass-jewelry-reflection-corrector/SKILL.md</t>
         </is>
       </c>
-      <c r="L137" s="2" t="inlineStr">
+      <c r="N137" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8465,10 +9837,20 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
           <t>skills/digital-3c-explosion-exploded-view/SKILL.md</t>
         </is>
       </c>
-      <c r="L138" s="2" t="inlineStr">
+      <c r="N138" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8523,10 +9905,20 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
           <t>skills/fresh-food-steam-appetite-enhancer/SKILL.md</t>
         </is>
       </c>
-      <c r="L139" s="2" t="inlineStr">
+      <c r="N139" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8581,10 +9973,20 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
           <t>skills/furniture-nordic-interior-stager/SKILL.md</t>
         </is>
       </c>
-      <c r="L140" s="2" t="inlineStr">
+      <c r="N140" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8639,10 +10041,20 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
           <t>skills/capcut-viral-sales-video-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L141" s="2" t="inlineStr">
+      <c r="N141" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8697,10 +10109,20 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
           <t>skills/heygen-global-avatar-spokesperson/SKILL.md</t>
         </is>
       </c>
-      <c r="L142" s="2" t="inlineStr">
+      <c r="N142" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8755,10 +10177,20 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
           <t>skills/did-photo-talking-presenter/SKILL.md</t>
         </is>
       </c>
-      <c r="L143" s="2" t="inlineStr">
+      <c r="N143" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8813,10 +10245,20 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
           <t>skills/invideo-prompt-to-ecom-video/SKILL.md</t>
         </is>
       </c>
-      <c r="L144" s="2" t="inlineStr">
+      <c r="N144" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8871,10 +10313,20 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
           <t>skills/vrew-text-to-video-voiceover-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L145" s="2" t="inlineStr">
+      <c r="N145" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8929,10 +10381,20 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
           <t>skills/captions-talking-head-eye-fixer/SKILL.md</t>
         </is>
       </c>
-      <c r="L146" s="2" t="inlineStr">
+      <c r="N146" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -8987,10 +10449,20 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
           <t>skills/submagic-shorts-broll-enhancer/SKILL.md</t>
         </is>
       </c>
-      <c r="L147" s="2" t="inlineStr">
+      <c r="N147" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9045,10 +10517,20 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-product-main-video-crafter/SKILL.md</t>
         </is>
       </c>
-      <c r="L148" s="2" t="inlineStr">
+      <c r="N148" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9103,10 +10585,20 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
           <t>skills/opusclip-livestream-to-shorts-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L149" s="2" t="inlineStr">
+      <c r="N149" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9161,10 +10653,20 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
           <t>skills/runway-cinematic-liquid-smoke-fx/SKILL.md</t>
         </is>
       </c>
-      <c r="L150" s="2" t="inlineStr">
+      <c r="N150" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9219,10 +10721,20 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
           <t>skills/sellersprite-keyword-blueocean-miner/SKILL.md</t>
         </is>
       </c>
-      <c r="L151" s="2" t="inlineStr">
+      <c r="N151" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9277,10 +10789,20 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
           <t>skills/helium10-cerebro-asin-reverse-spy/SKILL.md</t>
         </is>
       </c>
-      <c r="L152" s="2" t="inlineStr">
+      <c r="N152" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9335,10 +10857,20 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
           <t>skills/fastmoss-tiktok-viral-creator-spy/SKILL.md</t>
         </is>
       </c>
-      <c r="L153" s="2" t="inlineStr">
+      <c r="N153" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9393,10 +10925,20 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
           <t>skills/echotik-category-trend-predictor/SKILL.md</t>
         </is>
       </c>
-      <c r="L154" s="2" t="inlineStr">
+      <c r="N154" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9451,10 +10993,20 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
           <t>skills/kalodata-script-revenue-calculator/SKILL.md</t>
         </is>
       </c>
-      <c r="L155" s="2" t="inlineStr">
+      <c r="N155" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9509,10 +11061,20 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
           <t>skills/shopeefans-sea-multistore-autopilot/SKILL.md</t>
         </is>
       </c>
-      <c r="L156" s="2" t="inlineStr">
+      <c r="N156" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9567,10 +11129,20 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
           <t>skills/shoplus-winning-landing-page-spy/SKILL.md</t>
         </is>
       </c>
-      <c r="L157" s="2" t="inlineStr">
+      <c r="N157" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9625,10 +11197,20 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
           <t>skills/modash-influencer-fake-follower-checker/SKILL.md</t>
         </is>
       </c>
-      <c r="L158" s="2" t="inlineStr">
+      <c r="N158" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9683,10 +11265,20 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
           <t>skills/upfluence-influencer-batch-outreach/SKILL.md</t>
         </is>
       </c>
-      <c r="L159" s="2" t="inlineStr">
+      <c r="N159" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9741,10 +11333,20 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
           <t>skills/qiangua-rednote-trend-keyword-miner/SKILL.md</t>
         </is>
       </c>
-      <c r="L160" s="2" t="inlineStr">
+      <c r="N160" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9799,10 +11401,20 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
           <t>skills/copyai-amazon-five-bulletpoints-pro/SKILL.md</t>
         </is>
       </c>
-      <c r="L161" s="2" t="inlineStr">
+      <c r="N161" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9857,10 +11469,20 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
           <t>skills/jasper-dtc-brand-storytelling-engine/SKILL.md</t>
         </is>
       </c>
-      <c r="L162" s="2" t="inlineStr">
+      <c r="N162" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9915,10 +11537,20 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
           <t>skills/surfer-seo-ecommerce-rank-booster/SKILL.md</t>
         </is>
       </c>
-      <c r="L163" s="2" t="inlineStr">
+      <c r="N163" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -9973,10 +11605,20 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
           <t>skills/grammarly-seller-support-proofreader/SKILL.md</t>
         </is>
       </c>
-      <c r="L164" s="2" t="inlineStr">
+      <c r="N164" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10031,10 +11673,20 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-a-plus-ebc-visual-copy-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L165" s="2" t="inlineStr">
+      <c r="N165" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10089,10 +11741,20 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-voc-negative-review-analyzer/SKILL.md</t>
         </is>
       </c>
-      <c r="L166" s="2" t="inlineStr">
+      <c r="N166" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10147,10 +11809,20 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
           <t>skills/ecommerce-buyer-qa-objection-killer/SKILL.md</t>
         </is>
       </c>
-      <c r="L167" s="2" t="inlineStr">
+      <c r="N167" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10205,10 +11877,20 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
           <t>skills/black-friday-promo-urgency-copywriter/SKILL.md</t>
         </is>
       </c>
-      <c r="L168" s="2" t="inlineStr">
+      <c r="N168" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10263,10 +11945,20 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
           <t>skills/multilingual-user-manual-translator/SKILL.md</t>
         </is>
       </c>
-      <c r="L169" s="2" t="inlineStr">
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10321,10 +12013,20 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-semi-hosted-image-compliance/SKILL.md</t>
         </is>
       </c>
-      <c r="L170" s="2" t="inlineStr">
+      <c r="N170" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10379,10 +12081,20 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-flatlay-spec-generator/SKILL.md</t>
         </is>
       </c>
-      <c r="L171" s="2" t="inlineStr">
+      <c r="N171" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10437,10 +12149,20 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
           <t>skills/ozon-infographic-russian-rich-content/SKILL.md</t>
         </is>
       </c>
-      <c r="L172" s="2" t="inlineStr">
+      <c r="N172" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10495,10 +12217,20 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
           <t>skills/1688-crossborder-data-pack-exporter/SKILL.md</t>
         </is>
       </c>
-      <c r="L173" s="2" t="inlineStr">
+      <c r="N173" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10553,10 +12285,20 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
           <t>skills/walmart-marketplace-spec-asset-pack/SKILL.md</t>
         </is>
       </c>
-      <c r="L174" s="2" t="inlineStr">
+      <c r="N174" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10611,10 +12353,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
           <t>skills/etsy-vintage-handcrafted-aesthetic-shot/SKILL.md</t>
         </is>
       </c>
-      <c r="L175" s="2" t="inlineStr">
+      <c r="N175" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10669,10 +12421,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
           <t>skills/dianxiaomi-bulk-catalog-formatter/SKILL.md</t>
         </is>
       </c>
-      <c r="L176" s="2" t="inlineStr">
+      <c r="N176" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10727,10 +12489,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
           <t>skills/meta-carousel-ad-creative-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L177" s="2" t="inlineStr">
+      <c r="N177" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10785,10 +12557,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
           <t>skills/flux-lora-product-scene-renderer/SKILL.md</t>
         </is>
       </c>
-      <c r="L178" s="2" t="inlineStr">
+      <c r="N178" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10843,10 +12625,20 @@
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
           <t>skills/cli-batch-image-processor-engine/SKILL.md</t>
         </is>
       </c>
-      <c r="L179" s="2" t="inlineStr">
+      <c r="N179" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10901,10 +12693,20 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
           <t>skills/comfyui-ecommerce-outpainting-node/SKILL.md</t>
         </is>
       </c>
-      <c r="L180" s="2" t="inlineStr">
+      <c r="N180" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -10959,10 +12761,20 @@
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
           <t>skills/controlnet-pose-fashion-stabilizer/SKILL.md</t>
         </is>
       </c>
-      <c r="L181" s="2" t="inlineStr">
+      <c r="N181" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11017,10 +12829,20 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
           <t>skills/segment-anything-garment-extractor/SKILL.md</t>
         </is>
       </c>
-      <c r="L182" s="2" t="inlineStr">
+      <c r="N182" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11075,10 +12897,20 @@
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
           <t>skills/christmas-holiday-product-theme-stager/SKILL.md</t>
         </is>
       </c>
-      <c r="L183" s="2" t="inlineStr">
+      <c r="N183" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11133,10 +12965,20 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
           <t>skills/halloween-party-spooky-scene-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L184" s="2" t="inlineStr">
+      <c r="N184" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11191,10 +13033,20 @@
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
           <t>skills/summer-beach-outdoor-sunshine-setter/SKILL.md</t>
         </is>
       </c>
-      <c r="L185" s="2" t="inlineStr">
+      <c r="N185" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11249,10 +13101,20 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
           <t>skills/valentines-romantic-gift-stage/SKILL.md</t>
         </is>
       </c>
-      <c r="L186" s="2" t="inlineStr">
+      <c r="N186" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11307,10 +13169,20 @@
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
           <t>skills/back-to-school-stationery-stager/SKILL.md</t>
         </is>
       </c>
-      <c r="L187" s="2" t="inlineStr">
+      <c r="N187" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11365,10 +13237,20 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
           <t>skills/ugc-creator-review-video-cloner/SKILL.md</t>
         </is>
       </c>
-      <c r="L188" s="2" t="inlineStr">
+      <c r="N188" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11423,10 +13305,20 @@
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
           <t>skills/editorial-street-fashion-shot/SKILL.md</t>
         </is>
       </c>
-      <c r="L189" s="2" t="inlineStr">
+      <c r="N189" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11481,10 +13373,20 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
           <t>skills/sneakers-floating-levitation-stage/SKILL.md</t>
         </is>
       </c>
-      <c r="L190" s="2" t="inlineStr">
+      <c r="N190" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11539,10 +13441,20 @@
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
           <t>skills/skincare-texture-swatch-smear-art/SKILL.md</t>
         </is>
       </c>
-      <c r="L191" s="2" t="inlineStr">
+      <c r="N191" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11597,10 +13509,20 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
           <t>skills/flash-sale-countdown-badge-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L192" s="2" t="inlineStr">
+      <c r="N192" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11655,10 +13577,20 @@
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-gmv-spike-detector/SKILL.md</t>
         </is>
       </c>
-      <c r="L193" s="2" t="inlineStr">
+      <c r="N193" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11713,10 +13645,20 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
           <t>skills/ecom-image-metadata-exif-stripper/SKILL.md</t>
         </is>
       </c>
-      <c r="L194" s="2" t="inlineStr">
+      <c r="N194" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11771,10 +13713,20 @@
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
           <t>skills/aliexpress-choice-badge-asset-suite/SKILL.md</t>
         </is>
       </c>
-      <c r="L195" s="2" t="inlineStr">
+      <c r="N195" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11829,10 +13781,20 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-weshop-mannequin-model-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L196" s="2" t="inlineStr">
+      <c r="N196" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11887,10 +13849,20 @@
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-kreado-ethnicity-model-swapper/SKILL.md</t>
         </is>
       </c>
-      <c r="L197" s="2" t="inlineStr">
+      <c r="N197" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -11945,10 +13917,20 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-vmodel-flatlay-tryon-crafter/SKILL.md</t>
         </is>
       </c>
-      <c r="L198" s="2" t="inlineStr">
+      <c r="N198" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12003,10 +13985,20 @@
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-photoroom-white-bg-complier/SKILL.md</t>
         </is>
       </c>
-      <c r="L199" s="2" t="inlineStr">
+      <c r="N199" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12061,10 +14053,20 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-flair-lifestyle-scene-stager/SKILL.md</t>
         </is>
       </c>
-      <c r="L200" s="2" t="inlineStr">
+      <c r="N200" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12119,10 +14121,20 @@
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-clipdrop-4k-upscale-enhancer/SKILL.md</t>
         </is>
       </c>
-      <c r="L201" s="2" t="inlineStr">
+      <c r="N201" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12177,10 +14189,20 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-pixelcut-mobile-to-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L202" s="2" t="inlineStr">
+      <c r="N202" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12235,10 +14257,20 @@
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-picwish-batch-sku-cutout/SKILL.md</t>
         </is>
       </c>
-      <c r="L203" s="2" t="inlineStr">
+      <c r="N203" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12293,10 +14325,20 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-capcut-viral-sales-shorts/SKILL.md</t>
         </is>
       </c>
-      <c r="L204" s="2" t="inlineStr">
+      <c r="N204" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12351,10 +14393,20 @@
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-heygen-avatar-sales-anchor/SKILL.md</t>
         </is>
       </c>
-      <c r="L205" s="2" t="inlineStr">
+      <c r="N205" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12409,10 +14461,20 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-invideo-text-to-video-ad/SKILL.md</t>
         </is>
       </c>
-      <c r="L206" s="2" t="inlineStr">
+      <c r="N206" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12467,10 +14529,20 @@
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-captions-eye-contact-subtitles/SKILL.md</t>
         </is>
       </c>
-      <c r="L207" s="2" t="inlineStr">
+      <c r="N207" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12525,10 +14597,20 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-sellersprite-blueocean-keywords/SKILL.md</t>
         </is>
       </c>
-      <c r="L208" s="2" t="inlineStr">
+      <c r="N208" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12583,10 +14665,20 @@
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-helium10-asin-traffic-spy/SKILL.md</t>
         </is>
       </c>
-      <c r="L209" s="2" t="inlineStr">
+      <c r="N209" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12641,10 +14733,20 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-copyai-five-bulletpoints/SKILL.md</t>
         </is>
       </c>
-      <c r="L210" s="2" t="inlineStr">
+      <c r="N210" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12699,10 +14801,20 @@
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-deepl-native-localizer/SKILL.md</t>
         </is>
       </c>
-      <c r="L211" s="2" t="inlineStr">
+      <c r="N211" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12757,10 +14869,20 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-voc-review-insight-digger/SKILL.md</t>
         </is>
       </c>
-      <c r="L212" s="2" t="inlineStr">
+      <c r="N212" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12815,10 +14937,20 @@
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-promo-urgency-badge-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L213" s="2" t="inlineStr">
+      <c r="N213" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12873,10 +15005,20 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-rich-content-aplus-builder/SKILL.md</t>
         </is>
       </c>
-      <c r="L214" s="2" t="inlineStr">
+      <c r="N214" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12931,10 +15073,20 @@
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
           <t>skills/amazon-us-modash-creator-outreach-pilot/SKILL.md</t>
         </is>
       </c>
-      <c r="L215" s="2" t="inlineStr">
+      <c r="N215" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -12989,10 +15141,20 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-weshop-mannequin-model-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L216" s="2" t="inlineStr">
+      <c r="N216" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13047,10 +15209,20 @@
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-kreado-ethnicity-model-swapper/SKILL.md</t>
         </is>
       </c>
-      <c r="L217" s="2" t="inlineStr">
+      <c r="N217" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13105,10 +15277,20 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-vmodel-flatlay-tryon-crafter/SKILL.md</t>
         </is>
       </c>
-      <c r="L218" s="2" t="inlineStr">
+      <c r="N218" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13163,10 +15345,20 @@
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-photoroom-white-bg-complier/SKILL.md</t>
         </is>
       </c>
-      <c r="L219" s="2" t="inlineStr">
+      <c r="N219" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13221,10 +15413,20 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-flair-lifestyle-scene-stager/SKILL.md</t>
         </is>
       </c>
-      <c r="L220" s="2" t="inlineStr">
+      <c r="N220" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13279,10 +15481,20 @@
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-clipdrop-4k-upscale-enhancer/SKILL.md</t>
         </is>
       </c>
-      <c r="L221" s="2" t="inlineStr">
+      <c r="N221" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13337,10 +15549,20 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-pixelcut-mobile-to-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L222" s="2" t="inlineStr">
+      <c r="N222" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13395,10 +15617,20 @@
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-picwish-batch-sku-cutout/SKILL.md</t>
         </is>
       </c>
-      <c r="L223" s="2" t="inlineStr">
+      <c r="N223" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13453,10 +15685,20 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-capcut-viral-sales-shorts/SKILL.md</t>
         </is>
       </c>
-      <c r="L224" s="2" t="inlineStr">
+      <c r="N224" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13511,10 +15753,20 @@
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-heygen-avatar-sales-anchor/SKILL.md</t>
         </is>
       </c>
-      <c r="L225" s="2" t="inlineStr">
+      <c r="N225" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13569,10 +15821,20 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-invideo-text-to-video-ad/SKILL.md</t>
         </is>
       </c>
-      <c r="L226" s="2" t="inlineStr">
+      <c r="N226" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13627,10 +15889,20 @@
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-captions-eye-contact-subtitles/SKILL.md</t>
         </is>
       </c>
-      <c r="L227" s="2" t="inlineStr">
+      <c r="N227" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13685,10 +15957,20 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-sellersprite-blueocean-keywords/SKILL.md</t>
         </is>
       </c>
-      <c r="L228" s="2" t="inlineStr">
+      <c r="N228" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13743,10 +16025,20 @@
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-helium10-asin-traffic-spy/SKILL.md</t>
         </is>
       </c>
-      <c r="L229" s="2" t="inlineStr">
+      <c r="N229" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13801,10 +16093,20 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-copyai-five-bulletpoints/SKILL.md</t>
         </is>
       </c>
-      <c r="L230" s="2" t="inlineStr">
+      <c r="N230" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13859,10 +16161,20 @@
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-deepl-native-localizer/SKILL.md</t>
         </is>
       </c>
-      <c r="L231" s="2" t="inlineStr">
+      <c r="N231" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13917,10 +16229,20 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-voc-review-insight-digger/SKILL.md</t>
         </is>
       </c>
-      <c r="L232" s="2" t="inlineStr">
+      <c r="N232" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -13975,10 +16297,20 @@
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-promo-urgency-badge-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L233" s="2" t="inlineStr">
+      <c r="N233" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14033,10 +16365,20 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-rich-content-aplus-builder/SKILL.md</t>
         </is>
       </c>
-      <c r="L234" s="2" t="inlineStr">
+      <c r="N234" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14091,10 +16433,20 @@
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="inlineStr">
+        <is>
           <t>skills/tiktok-shop-modash-creator-outreach-pilot/SKILL.md</t>
         </is>
       </c>
-      <c r="L235" s="2" t="inlineStr">
+      <c r="N235" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14149,10 +16501,20 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-weshop-mannequin-model-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L236" s="2" t="inlineStr">
+      <c r="N236" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14207,10 +16569,20 @@
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-kreado-ethnicity-model-swapper/SKILL.md</t>
         </is>
       </c>
-      <c r="L237" s="2" t="inlineStr">
+      <c r="N237" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14265,10 +16637,20 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-vmodel-flatlay-tryon-crafter/SKILL.md</t>
         </is>
       </c>
-      <c r="L238" s="2" t="inlineStr">
+      <c r="N238" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14323,10 +16705,20 @@
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-photoroom-white-bg-complier/SKILL.md</t>
         </is>
       </c>
-      <c r="L239" s="2" t="inlineStr">
+      <c r="N239" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14381,10 +16773,20 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-flair-lifestyle-scene-stager/SKILL.md</t>
         </is>
       </c>
-      <c r="L240" s="2" t="inlineStr">
+      <c r="N240" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14439,10 +16841,20 @@
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-clipdrop-4k-upscale-enhancer/SKILL.md</t>
         </is>
       </c>
-      <c r="L241" s="2" t="inlineStr">
+      <c r="N241" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14497,10 +16909,20 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-pixelcut-mobile-to-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L242" s="2" t="inlineStr">
+      <c r="N242" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14555,10 +16977,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-picwish-batch-sku-cutout/SKILL.md</t>
         </is>
       </c>
-      <c r="L243" s="2" t="inlineStr">
+      <c r="N243" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14613,10 +17045,20 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-capcut-viral-sales-shorts/SKILL.md</t>
         </is>
       </c>
-      <c r="L244" s="2" t="inlineStr">
+      <c r="N244" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14671,10 +17113,20 @@
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-heygen-avatar-sales-anchor/SKILL.md</t>
         </is>
       </c>
-      <c r="L245" s="2" t="inlineStr">
+      <c r="N245" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14729,10 +17181,20 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-invideo-text-to-video-ad/SKILL.md</t>
         </is>
       </c>
-      <c r="L246" s="2" t="inlineStr">
+      <c r="N246" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14787,10 +17249,20 @@
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-captions-eye-contact-subtitles/SKILL.md</t>
         </is>
       </c>
-      <c r="L247" s="2" t="inlineStr">
+      <c r="N247" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14845,10 +17317,20 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-sellersprite-blueocean-keywords/SKILL.md</t>
         </is>
       </c>
-      <c r="L248" s="2" t="inlineStr">
+      <c r="N248" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14903,10 +17385,20 @@
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-helium10-asin-traffic-spy/SKILL.md</t>
         </is>
       </c>
-      <c r="L249" s="2" t="inlineStr">
+      <c r="N249" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -14961,10 +17453,20 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-copyai-five-bulletpoints/SKILL.md</t>
         </is>
       </c>
-      <c r="L250" s="2" t="inlineStr">
+      <c r="N250" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15019,10 +17521,20 @@
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-deepl-native-localizer/SKILL.md</t>
         </is>
       </c>
-      <c r="L251" s="2" t="inlineStr">
+      <c r="N251" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15077,10 +17589,20 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-voc-review-insight-digger/SKILL.md</t>
         </is>
       </c>
-      <c r="L252" s="2" t="inlineStr">
+      <c r="N252" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15135,10 +17657,20 @@
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-promo-urgency-badge-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L253" s="2" t="inlineStr">
+      <c r="N253" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15193,10 +17725,20 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-rich-content-aplus-builder/SKILL.md</t>
         </is>
       </c>
-      <c r="L254" s="2" t="inlineStr">
+      <c r="N254" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15251,10 +17793,20 @@
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="inlineStr">
+        <is>
           <t>skills/shopee-sea-modash-creator-outreach-pilot/SKILL.md</t>
         </is>
       </c>
-      <c r="L255" s="2" t="inlineStr">
+      <c r="N255" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15309,10 +17861,20 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-weshop-mannequin-model-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L256" s="2" t="inlineStr">
+      <c r="N256" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15367,10 +17929,20 @@
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-kreado-ethnicity-model-swapper/SKILL.md</t>
         </is>
       </c>
-      <c r="L257" s="2" t="inlineStr">
+      <c r="N257" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15425,10 +17997,20 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-vmodel-flatlay-tryon-crafter/SKILL.md</t>
         </is>
       </c>
-      <c r="L258" s="2" t="inlineStr">
+      <c r="N258" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15483,10 +18065,20 @@
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-photoroom-white-bg-complier/SKILL.md</t>
         </is>
       </c>
-      <c r="L259" s="2" t="inlineStr">
+      <c r="N259" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15541,10 +18133,20 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-flair-lifestyle-scene-stager/SKILL.md</t>
         </is>
       </c>
-      <c r="L260" s="2" t="inlineStr">
+      <c r="N260" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15599,10 +18201,20 @@
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-clipdrop-4k-upscale-enhancer/SKILL.md</t>
         </is>
       </c>
-      <c r="L261" s="2" t="inlineStr">
+      <c r="N261" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15657,10 +18269,20 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-pixelcut-mobile-to-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L262" s="2" t="inlineStr">
+      <c r="N262" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15715,10 +18337,20 @@
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-picwish-batch-sku-cutout/SKILL.md</t>
         </is>
       </c>
-      <c r="L263" s="2" t="inlineStr">
+      <c r="N263" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15773,10 +18405,20 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-capcut-viral-sales-shorts/SKILL.md</t>
         </is>
       </c>
-      <c r="L264" s="2" t="inlineStr">
+      <c r="N264" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15831,10 +18473,20 @@
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-heygen-avatar-sales-anchor/SKILL.md</t>
         </is>
       </c>
-      <c r="L265" s="2" t="inlineStr">
+      <c r="N265" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15889,10 +18541,20 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-invideo-text-to-video-ad/SKILL.md</t>
         </is>
       </c>
-      <c r="L266" s="2" t="inlineStr">
+      <c r="N266" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -15947,10 +18609,20 @@
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-captions-eye-contact-subtitles/SKILL.md</t>
         </is>
       </c>
-      <c r="L267" s="2" t="inlineStr">
+      <c r="N267" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16005,10 +18677,20 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-sellersprite-blueocean-keywords/SKILL.md</t>
         </is>
       </c>
-      <c r="L268" s="2" t="inlineStr">
+      <c r="N268" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16063,10 +18745,20 @@
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-helium10-asin-traffic-spy/SKILL.md</t>
         </is>
       </c>
-      <c r="L269" s="2" t="inlineStr">
+      <c r="N269" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16121,10 +18813,20 @@
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-copyai-five-bulletpoints/SKILL.md</t>
         </is>
       </c>
-      <c r="L270" s="2" t="inlineStr">
+      <c r="N270" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16179,10 +18881,20 @@
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-deepl-native-localizer/SKILL.md</t>
         </is>
       </c>
-      <c r="L271" s="2" t="inlineStr">
+      <c r="N271" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16237,10 +18949,20 @@
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M272" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-voc-review-insight-digger/SKILL.md</t>
         </is>
       </c>
-      <c r="L272" s="2" t="inlineStr">
+      <c r="N272" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16295,10 +19017,20 @@
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-promo-urgency-badge-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L273" s="2" t="inlineStr">
+      <c r="N273" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16353,10 +19085,20 @@
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-rich-content-aplus-builder/SKILL.md</t>
         </is>
       </c>
-      <c r="L274" s="2" t="inlineStr">
+      <c r="N274" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16411,10 +19153,20 @@
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="inlineStr">
+        <is>
           <t>skills/temu-host-modash-creator-outreach-pilot/SKILL.md</t>
         </is>
       </c>
-      <c r="L275" s="2" t="inlineStr">
+      <c r="N275" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16469,10 +19221,20 @@
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-weshop-mannequin-model-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L276" s="2" t="inlineStr">
+      <c r="N276" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16527,10 +19289,20 @@
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-kreado-ethnicity-model-swapper/SKILL.md</t>
         </is>
       </c>
-      <c r="L277" s="2" t="inlineStr">
+      <c r="N277" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16585,10 +19357,20 @@
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-vmodel-flatlay-tryon-crafter/SKILL.md</t>
         </is>
       </c>
-      <c r="L278" s="2" t="inlineStr">
+      <c r="N278" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16643,10 +19425,20 @@
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-photoroom-white-bg-complier/SKILL.md</t>
         </is>
       </c>
-      <c r="L279" s="2" t="inlineStr">
+      <c r="N279" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16701,10 +19493,20 @@
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-flair-lifestyle-scene-stager/SKILL.md</t>
         </is>
       </c>
-      <c r="L280" s="2" t="inlineStr">
+      <c r="N280" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16759,10 +19561,20 @@
       </c>
       <c r="K281" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-clipdrop-4k-upscale-enhancer/SKILL.md</t>
         </is>
       </c>
-      <c r="L281" s="2" t="inlineStr">
+      <c r="N281" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16817,10 +19629,20 @@
       </c>
       <c r="K282" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-pixelcut-mobile-to-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L282" s="2" t="inlineStr">
+      <c r="N282" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16875,10 +19697,20 @@
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-picwish-batch-sku-cutout/SKILL.md</t>
         </is>
       </c>
-      <c r="L283" s="2" t="inlineStr">
+      <c r="N283" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16933,10 +19765,20 @@
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-capcut-viral-sales-shorts/SKILL.md</t>
         </is>
       </c>
-      <c r="L284" s="2" t="inlineStr">
+      <c r="N284" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -16991,10 +19833,20 @@
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-heygen-avatar-sales-anchor/SKILL.md</t>
         </is>
       </c>
-      <c r="L285" s="2" t="inlineStr">
+      <c r="N285" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17049,10 +19901,20 @@
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-invideo-text-to-video-ad/SKILL.md</t>
         </is>
       </c>
-      <c r="L286" s="2" t="inlineStr">
+      <c r="N286" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17107,10 +19969,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-captions-eye-contact-subtitles/SKILL.md</t>
         </is>
       </c>
-      <c r="L287" s="2" t="inlineStr">
+      <c r="N287" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17165,10 +20037,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-sellersprite-blueocean-keywords/SKILL.md</t>
         </is>
       </c>
-      <c r="L288" s="2" t="inlineStr">
+      <c r="N288" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17223,10 +20105,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-helium10-asin-traffic-spy/SKILL.md</t>
         </is>
       </c>
-      <c r="L289" s="2" t="inlineStr">
+      <c r="N289" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17281,10 +20173,20 @@
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-copyai-five-bulletpoints/SKILL.md</t>
         </is>
       </c>
-      <c r="L290" s="2" t="inlineStr">
+      <c r="N290" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17339,10 +20241,20 @@
       </c>
       <c r="K291" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-deepl-native-localizer/SKILL.md</t>
         </is>
       </c>
-      <c r="L291" s="2" t="inlineStr">
+      <c r="N291" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17397,10 +20309,20 @@
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-voc-review-insight-digger/SKILL.md</t>
         </is>
       </c>
-      <c r="L292" s="2" t="inlineStr">
+      <c r="N292" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17455,10 +20377,20 @@
       </c>
       <c r="K293" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-promo-urgency-badge-maker/SKILL.md</t>
         </is>
       </c>
-      <c r="L293" s="2" t="inlineStr">
+      <c r="N293" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17513,10 +20445,20 @@
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-rich-content-aplus-builder/SKILL.md</t>
         </is>
       </c>
-      <c r="L294" s="2" t="inlineStr">
+      <c r="N294" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17571,10 +20513,20 @@
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="inlineStr">
+        <is>
           <t>skills/shein-apparel-modash-creator-outreach-pilot/SKILL.md</t>
         </is>
       </c>
-      <c r="L295" s="2" t="inlineStr">
+      <c r="N295" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17629,10 +20581,20 @@
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr">
+        <is>
           <t>skills/shopify-dtc-weshop-mannequin-model-studio/SKILL.md</t>
         </is>
       </c>
-      <c r="L296" s="2" t="inlineStr">
+      <c r="N296" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17687,10 +20649,20 @@
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="inlineStr">
+        <is>
           <t>skills/shopify-dtc-kreado-ethnicity-model-swapper/SKILL.md</t>
         </is>
       </c>
-      <c r="L297" s="2" t="inlineStr">
+      <c r="N297" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17745,10 +20717,20 @@
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr">
+        <is>
           <t>skills/shopify-dtc-vmodel-flatlay-tryon-crafter/SKILL.md</t>
         </is>
       </c>
-      <c r="L298" s="2" t="inlineStr">
+      <c r="N298" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17803,10 +20785,20 @@
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="inlineStr">
+        <is>
           <t>skills/shopify-dtc-photoroom-white-bg-complier/SKILL.md</t>
         </is>
       </c>
-      <c r="L299" s="2" t="inlineStr">
+      <c r="N299" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17861,10 +20853,20 @@
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="inlineStr">
+        <is>
           <t>skills/shopify-dtc-flair-lifestyle-scene-stager/SKILL.md</t>
         </is>
       </c>
-      <c r="L300" s="2" t="inlineStr">
+      <c r="N300" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
@@ -17919,10 +20921,20 @@
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="L301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iqinghu.com/workbench/login?type=1&amp;urlCode=1788417527636</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="inlineStr">
+        <is>
           <t>skills/shopify-dtc-clipdrop-4k-upscale-enhancer/SKILL.md</t>
         </is>
       </c>
-      <c r="L301" s="2" t="inlineStr">
+      <c r="N301" s="2" t="inlineStr">
         <is>
           <t>published_v1</t>
         </is>
